--- a/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times_success.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times_success.xlsx
@@ -413,21 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>pd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>hopa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>gdpa-100</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gdpa-200</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>bf</t>
         </is>
@@ -438,13 +448,19 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0003413284383714199</v>
+        <v>0.0001368683949112892</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002619666792452336</v>
+        <v>0.0003360499907284975</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4560358345508576</v>
+        <v>0.0003301798645406961</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0002777300029993057</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4582752680778504</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +468,19 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0003799166902899742</v>
+        <v>0.0001394066866487265</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0003014316689223051</v>
+        <v>0.0003211833164095879</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3546077561378479</v>
+        <v>0.0002941682934761047</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0002357499673962593</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3540511178970337</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +488,19 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0003712850343436003</v>
+        <v>0.0001401899103075266</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002817266713827849</v>
+        <v>0.0003370282426476479</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3143586891889572</v>
+        <v>0.0003079382609575987</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.000261054914444685</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.315459703207016</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +508,19 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0009825183544307948</v>
+        <v>0.0001490017457399517</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005974982306361198</v>
+        <v>0.0005986049771308898</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3034147179126739</v>
+        <v>0.0008618883974850178</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0008090117573738098</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3047110742330551</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +528,19 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.003570451801642776</v>
+        <v>0.0001364639558067376</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003299361690878868</v>
+        <v>0.0005681800376623869</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3348790818452835</v>
+        <v>0.002960000038146973</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.002818504963070154</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3350402837991714</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +548,19 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.009993974985554814</v>
+        <v>0.0001559583581097069</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009737256718799471</v>
+        <v>0.0006715099234133959</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3741119164228439</v>
+        <v>0.009925934663042426</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01000043971464038</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3732976883649826</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +568,19 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03307399030774832</v>
+        <v>0.0001937441217402617</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03369759494438768</v>
+        <v>0.0007894721056800336</v>
       </c>
       <c r="D8" t="n">
-        <v>0.468177964091301</v>
+        <v>0.03553116578608751</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.03609641855582595</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4728059631586075</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>1.414537314819172</v>
+        <v>0.0001866111376633247</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8470635627955199</v>
+        <v>0.01529674270105633</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3641132539510727</v>
+        <v>0.8621151719521731</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8386285943444818</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3602443265914917</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.07037876049987972</v>
+        <v>0.000136157580917435</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06728185413405299</v>
+        <v>0.01123826384233932</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3033003252744675</v>
+        <v>0.06935173191130162</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.06114743678830564</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3005736583471298</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1033307997956096</v>
+        <v>0.0001769167032431473</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3711445397883654</v>
+        <v>0.02890039420453832</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2524626421928406</v>
+        <v>0.1072572763174928</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3765220335498452</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2494030541181564</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5422964268768935</v>
+        <v>0.0002864947600755841</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5366637182077798</v>
+        <v>0.03038788940757513</v>
       </c>
       <c r="D12" t="n">
-        <v>0.343082720041275</v>
+        <v>0.5467411803749754</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4619103932915175</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3432255566120148</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6664342825533822</v>
+        <v>0.0003362221565718452</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5870583821734827</v>
+        <v>0.01992641712006714</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3153763224060337</v>
+        <v>0.6495351542511748</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6463628795075541</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3173182178288698</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>47.13341408604497</v>
+        <v>0.0004225336480885744</v>
       </c>
       <c r="C14" t="n">
-        <v>46.73463962325413</v>
+        <v>0.001263816608116031</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3307508709638015</v>
+        <v>46.75391589621237</v>
+      </c>
+      <c r="E14" t="n">
+        <v>46.80349319122939</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3379825606294301</v>
       </c>
     </row>
     <row r="15">
@@ -620,97 +708,115 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>2.370206094550667</v>
+        <v>0.001442833105102181</v>
       </c>
       <c r="C15" t="n">
-        <v>3.426260271493126</v>
+        <v>0.004338833037763834</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2871181997268096</v>
+        <v>2.335998196809669</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.499938977156382</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3049165198336477</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>0.7947368421052632</v>
       </c>
-      <c r="B16" t="n">
-        <v>0.72148966209756</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.6795045708616575</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5376100621440194</v>
+        <v>0.6575313276714749</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6416967693302367</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5247801759026267</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>0.8157894736842105</v>
       </c>
-      <c r="B17" t="n">
-        <v>0.8251512120477855</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.7830688515678048</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.2218033887445927</v>
+        <v>0.7958792480640113</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7751213717274368</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2200568526983261</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>0.8368421052631578</v>
       </c>
-      <c r="B18" t="n">
-        <v>0.3629950812707345</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.3644617075721423</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>1.541900630295277</v>
+        <v>0.3577973693609238</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3476052079349756</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.73492241948843</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>0.8578947368421053</v>
       </c>
-      <c r="B19" t="n">
-        <v>0.5851727887988091</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.4952187513311704</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.2285135898150896</v>
+        <v>0.515645195171237</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.4999092466508349</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2307992734407124</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>0.8789473684210527</v>
       </c>
-      <c r="B20" t="n">
-        <v>0.4795207670993275</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.4630750089883804</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.3434773192686193</v>
+        <v>0.4747116077277396</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.4524914868175983</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3447703079265707</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>0.9</v>
       </c>
-      <c r="B21" t="n">
-        <v>0.7704963386058807</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.7690722122788429</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.2120547383092344</v>
+        <v>0.7534885611385107</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7357200253754854</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2074131825938821</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times_success.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times_success.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,15 +429,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>gdpa-prio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>gdpa-100</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gdpa-200</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>bf</t>
         </is>
@@ -454,12 +459,15 @@
         <v>0.0003360499907284975</v>
       </c>
       <c r="D2" t="n">
+        <v>0.0003416150342673063</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.0003301798645406961</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.0002777300029993057</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.4582752680778504</v>
       </c>
     </row>
@@ -474,12 +482,15 @@
         <v>0.0003211833164095879</v>
       </c>
       <c r="D3" t="n">
+        <v>0.0005295366048812866</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.0002941682934761047</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.0002357499673962593</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.3540511178970337</v>
       </c>
     </row>
@@ -494,12 +505,15 @@
         <v>0.0003370282426476479</v>
       </c>
       <c r="D4" t="n">
+        <v>0.000475651565939188</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.0003079382609575987</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.000261054914444685</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.315459703207016</v>
       </c>
     </row>
@@ -514,12 +528,15 @@
         <v>0.0005986049771308898</v>
       </c>
       <c r="D5" t="n">
+        <v>0.0004669700469821692</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.0008618883974850178</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.0008090117573738098</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.3047110742330551</v>
       </c>
     </row>
@@ -534,12 +551,15 @@
         <v>0.0005681800376623869</v>
       </c>
       <c r="D6" t="n">
+        <v>0.0009011666849255562</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.002960000038146973</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.002818504963070154</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.3350402837991714</v>
       </c>
     </row>
@@ -554,12 +574,15 @@
         <v>0.0006715099234133959</v>
       </c>
       <c r="D7" t="n">
+        <v>0.001730554969981313</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.009925934663042426</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.01000043971464038</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.3732976883649826</v>
       </c>
     </row>
@@ -574,12 +597,15 @@
         <v>0.0007894721056800336</v>
       </c>
       <c r="D8" t="n">
+        <v>0.002285326505079865</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.03553116578608751</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.03609641855582595</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.4728059631586075</v>
       </c>
     </row>
@@ -594,12 +620,15 @@
         <v>0.01529674270105633</v>
       </c>
       <c r="D9" t="n">
+        <v>0.005336568842682502</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.8621151719521731</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.8386285943444818</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.3602443265914917</v>
       </c>
     </row>
@@ -614,12 +643,15 @@
         <v>0.01123826384233932</v>
       </c>
       <c r="D10" t="n">
+        <v>0.00743332571900365</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.06935173191130162</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0.06114743678830564</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.3005736583471298</v>
       </c>
     </row>
@@ -634,12 +666,15 @@
         <v>0.02890039420453832</v>
       </c>
       <c r="D11" t="n">
+        <v>0.0172446082928218</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.1072572763174928</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.3765220335498452</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.2494030541181564</v>
       </c>
     </row>
@@ -654,12 +689,15 @@
         <v>0.03038788940757513</v>
       </c>
       <c r="D12" t="n">
+        <v>0.03064986971827845</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.5467411803749754</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.4619103932915175</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.3432255566120148</v>
       </c>
     </row>
@@ -674,12 +712,15 @@
         <v>0.01992641712006714</v>
       </c>
       <c r="D13" t="n">
+        <v>1.047740476930307</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.6495351542511748</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.6463628795075541</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0.3173182178288698</v>
       </c>
     </row>
@@ -694,12 +735,15 @@
         <v>0.001263816608116031</v>
       </c>
       <c r="D14" t="n">
+        <v>0.0009552082046866417</v>
+      </c>
+      <c r="E14" t="n">
         <v>46.75391589621237</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>46.80349319122939</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>0.3379825606294301</v>
       </c>
     </row>
@@ -714,12 +758,15 @@
         <v>0.004338833037763834</v>
       </c>
       <c r="D15" t="n">
+        <v>0.002980499994009733</v>
+      </c>
+      <c r="E15" t="n">
         <v>2.335998196809669</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>3.499938977156382</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.3049165198336477</v>
       </c>
     </row>
@@ -729,13 +776,14 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
         <v>0.6575313276714749</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>0.6416967693302367</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.5247801759026267</v>
       </c>
     </row>
@@ -745,13 +793,14 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="n">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
         <v>0.7958792480640113</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>0.7751213717274368</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.2200568526983261</v>
       </c>
     </row>
@@ -761,13 +810,14 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="n">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
         <v>0.3577973693609238</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>0.3476052079349756</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1.73492241948843</v>
       </c>
     </row>
@@ -777,13 +827,14 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
         <v>0.515645195171237</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.4999092466508349</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.2307992734407124</v>
       </c>
     </row>
@@ -793,13 +844,14 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="n">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
         <v>0.4747116077277396</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>0.4524914868175983</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.3447703079265707</v>
       </c>
     </row>
@@ -809,13 +861,14 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="n">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
         <v>0.7534885611385107</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0.7357200253754854</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0.2074131825938821</v>
       </c>
     </row>

--- a/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times_success.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times_success.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>gdpa-ms</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>bf</t>
         </is>
       </c>
@@ -468,6 +473,9 @@
         <v>0.0002777300029993057</v>
       </c>
       <c r="G2" t="n">
+        <v>0.0005483967438340187</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.4582752680778504</v>
       </c>
     </row>
@@ -491,6 +499,9 @@
         <v>0.0002357499673962593</v>
       </c>
       <c r="G3" t="n">
+        <v>0.0005519283376634121</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.3540511178970337</v>
       </c>
     </row>
@@ -514,6 +525,9 @@
         <v>0.000261054914444685</v>
       </c>
       <c r="G4" t="n">
+        <v>0.000723953228443861</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.315459703207016</v>
       </c>
     </row>
@@ -537,6 +551,9 @@
         <v>0.0008090117573738098</v>
       </c>
       <c r="G5" t="n">
+        <v>0.002200389998033643</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.3047110742330551</v>
       </c>
     </row>
@@ -560,6 +577,9 @@
         <v>0.002818504963070154</v>
       </c>
       <c r="G6" t="n">
+        <v>0.02261634830385446</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.3350402837991714</v>
       </c>
     </row>
@@ -583,6 +603,9 @@
         <v>0.01000043971464038</v>
       </c>
       <c r="G7" t="n">
+        <v>0.02381413975730538</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.3732976883649826</v>
       </c>
     </row>
@@ -606,6 +629,9 @@
         <v>0.03609641855582595</v>
       </c>
       <c r="G8" t="n">
+        <v>0.06260479481890797</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.4728059631586075</v>
       </c>
     </row>
@@ -629,6 +655,9 @@
         <v>0.8386285943444818</v>
       </c>
       <c r="G9" t="n">
+        <v>0.8339146154653281</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.3602443265914917</v>
       </c>
     </row>
@@ -652,6 +681,9 @@
         <v>0.06114743678830564</v>
       </c>
       <c r="G10" t="n">
+        <v>0.1941089734714478</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.3005736583471298</v>
       </c>
     </row>
@@ -675,6 +707,9 @@
         <v>0.3765220335498452</v>
       </c>
       <c r="G11" t="n">
+        <v>0.5128496505599469</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.2494030541181564</v>
       </c>
     </row>
@@ -698,6 +733,9 @@
         <v>0.4619103932915175</v>
       </c>
       <c r="G12" t="n">
+        <v>0.9833970176801086</v>
+      </c>
+      <c r="H12" t="n">
         <v>0.3432255566120148</v>
       </c>
     </row>
@@ -721,6 +759,9 @@
         <v>0.6463628795075541</v>
       </c>
       <c r="G13" t="n">
+        <v>3.775667044237101</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.3173182178288698</v>
       </c>
     </row>
@@ -744,6 +785,9 @@
         <v>46.80349319122939</v>
       </c>
       <c r="G14" t="n">
+        <v>39.39876882449481</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.3379825606294301</v>
       </c>
     </row>
@@ -767,6 +811,9 @@
         <v>3.499938977156382</v>
       </c>
       <c r="G15" t="n">
+        <v>7.654454769171855</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.3049165198336477</v>
       </c>
     </row>
@@ -784,6 +831,9 @@
         <v>0.6416967693302367</v>
       </c>
       <c r="G16" t="n">
+        <v>1.804092611230555</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.5247801759026267</v>
       </c>
     </row>
@@ -801,6 +851,9 @@
         <v>0.7751213717274368</v>
       </c>
       <c r="G17" t="n">
+        <v>2.097467828914523</v>
+      </c>
+      <c r="H17" t="n">
         <v>0.2200568526983261</v>
       </c>
     </row>
@@ -818,6 +871,9 @@
         <v>0.3476052079349756</v>
       </c>
       <c r="G18" t="n">
+        <v>18.28103201546603</v>
+      </c>
+      <c r="H18" t="n">
         <v>1.73492241948843</v>
       </c>
     </row>
@@ -835,6 +891,9 @@
         <v>0.4999092466508349</v>
       </c>
       <c r="G19" t="n">
+        <v>1.101798184216022</v>
+      </c>
+      <c r="H19" t="n">
         <v>0.2307992734407124</v>
       </c>
     </row>
@@ -852,6 +911,9 @@
         <v>0.4524914868175983</v>
       </c>
       <c r="G20" t="n">
+        <v>6.080933970212937</v>
+      </c>
+      <c r="H20" t="n">
         <v>0.3447703079265707</v>
       </c>
     </row>
@@ -869,6 +931,9 @@
         <v>0.7357200253754854</v>
       </c>
       <c r="G21" t="n">
+        <v>6.628975462700639</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.2074131825938821</v>
       </c>
     </row>

--- a/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times_success.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times_success.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>gdpa-ms</t>
+          <t>gdpa-500</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -467,13 +467,13 @@
         <v>0.0003416150342673063</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003301798645406961</v>
+        <v>0.0005095131509006023</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002777300029993057</v>
+        <v>0.0004423550423234701</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005483967438340187</v>
+        <v>0.0005191765818744898</v>
       </c>
       <c r="H2" t="n">
         <v>0.4582752680778504</v>
@@ -493,13 +493,13 @@
         <v>0.0005295366048812866</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002941682934761047</v>
+        <v>0.0006020266376435757</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002357499673962593</v>
+        <v>0.0004342267103493214</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005519283376634121</v>
+        <v>0.0003772150166332722</v>
       </c>
       <c r="H3" t="n">
         <v>0.3540511178970337</v>
@@ -519,13 +519,13 @@
         <v>0.000475651565939188</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003079382609575987</v>
+        <v>0.0005282367207109928</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000261054914444685</v>
+        <v>0.0004220350552350283</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000723953228443861</v>
+        <v>0.0004140883032232523</v>
       </c>
       <c r="H4" t="n">
         <v>0.315459703207016</v>
@@ -545,13 +545,13 @@
         <v>0.0004669700469821692</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008618883974850178</v>
+        <v>0.003011890146881342</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0008090117573738098</v>
+        <v>0.002882975013926625</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002200389998033643</v>
+        <v>0.002849804908037186</v>
       </c>
       <c r="H5" t="n">
         <v>0.3047110742330551</v>
@@ -571,13 +571,13 @@
         <v>0.0009011666849255562</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002960000038146973</v>
+        <v>0.02061164035461843</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002818504963070154</v>
+        <v>0.01963330503553152</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02261634830385446</v>
+        <v>0.01952877149917185</v>
       </c>
       <c r="H6" t="n">
         <v>0.3350402837991714</v>
@@ -597,13 +597,13 @@
         <v>0.001730554969981313</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009925934663042426</v>
+        <v>0.06939669345505535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01000043971464038</v>
+        <v>0.06639822180382908</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02381413975730538</v>
+        <v>0.06587546180002392</v>
       </c>
       <c r="H7" t="n">
         <v>0.3732976883649826</v>
@@ -623,13 +623,13 @@
         <v>0.002285326505079865</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03553116578608751</v>
+        <v>0.05126201952807605</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03609641855582595</v>
+        <v>0.04889098497107625</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06260479481890797</v>
+        <v>0.04821279509924352</v>
       </c>
       <c r="H8" t="n">
         <v>0.4728059631586075</v>
@@ -649,13 +649,13 @@
         <v>0.005336568842682502</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8621151719521731</v>
+        <v>0.8520767791382968</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8386285943444818</v>
+        <v>0.8216597569733858</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8339146154653281</v>
+        <v>0.8098553357459605</v>
       </c>
       <c r="H9" t="n">
         <v>0.3602443265914917</v>
@@ -675,13 +675,13 @@
         <v>0.00743332571900365</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06935173191130162</v>
+        <v>0.2429448819160461</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06114743678830564</v>
+        <v>0.2164601116813719</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1941089734714478</v>
+        <v>0.253818922424689</v>
       </c>
       <c r="H10" t="n">
         <v>0.3005736583471298</v>
@@ -701,13 +701,13 @@
         <v>0.0172446082928218</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1072572763174928</v>
+        <v>0.8011621759738773</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3765220335498452</v>
+        <v>0.7639709469955415</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5128496505599469</v>
+        <v>0.744724514465779</v>
       </c>
       <c r="H11" t="n">
         <v>0.2494030541181564</v>
@@ -727,13 +727,13 @@
         <v>0.03064986971827845</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5467411803749754</v>
+        <v>0.7005240148185597</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4619103932915175</v>
+        <v>1.086989105213434</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9833970176801086</v>
+        <v>1.644784434093162</v>
       </c>
       <c r="H12" t="n">
         <v>0.3432255566120148</v>
@@ -753,13 +753,13 @@
         <v>1.047740476930307</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6495351542511748</v>
+        <v>5.604443479615094</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6463628795075541</v>
+        <v>5.873018103155672</v>
       </c>
       <c r="G13" t="n">
-        <v>3.775667044237101</v>
+        <v>22.38240966261567</v>
       </c>
       <c r="H13" t="n">
         <v>0.3173182178288698</v>
@@ -779,13 +779,13 @@
         <v>0.0009552082046866417</v>
       </c>
       <c r="E14" t="n">
-        <v>46.75391589621237</v>
+        <v>5.390325625479983</v>
       </c>
       <c r="F14" t="n">
-        <v>46.80349319122939</v>
+        <v>5.021010163705796</v>
       </c>
       <c r="G14" t="n">
-        <v>39.39876882449481</v>
+        <v>4.325793117153175</v>
       </c>
       <c r="H14" t="n">
         <v>0.3379825606294301</v>
@@ -805,13 +805,13 @@
         <v>0.002980499994009733</v>
       </c>
       <c r="E15" t="n">
-        <v>2.335998196809669</v>
+        <v>24.4875236029648</v>
       </c>
       <c r="F15" t="n">
-        <v>3.499938977156382</v>
+        <v>25.42441758700824</v>
       </c>
       <c r="G15" t="n">
-        <v>7.654454769171855</v>
+        <v>18.67083825310692</v>
       </c>
       <c r="H15" t="n">
         <v>0.3049165198336477</v>
@@ -825,13 +825,13 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>0.6575313276714749</v>
+        <v>2.136124144867062</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6416967693302367</v>
+        <v>2.061709961011296</v>
       </c>
       <c r="G16" t="n">
-        <v>1.804092611230555</v>
+        <v>1.906207308882759</v>
       </c>
       <c r="H16" t="n">
         <v>0.5247801759026267</v>
@@ -845,13 +845,13 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>0.7958792480640113</v>
+        <v>1.399656784073967</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7751213717274368</v>
+        <v>2.608443131033135</v>
       </c>
       <c r="G17" t="n">
-        <v>2.097467828914523</v>
+        <v>1.480894748307765</v>
       </c>
       <c r="H17" t="n">
         <v>0.2200568526983261</v>
@@ -865,13 +865,13 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>0.3577973693609238</v>
+        <v>4.446204135815303</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3476052079349756</v>
+        <v>4.321799483564165</v>
       </c>
       <c r="G18" t="n">
-        <v>18.28103201546603</v>
+        <v>13.46389306038618</v>
       </c>
       <c r="H18" t="n">
         <v>1.73492241948843</v>
@@ -885,13 +885,13 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>0.515645195171237</v>
+        <v>2.200974995127091</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4999092466508349</v>
+        <v>4.102318050463994</v>
       </c>
       <c r="G19" t="n">
-        <v>1.101798184216022</v>
+        <v>8.957449585983628</v>
       </c>
       <c r="H19" t="n">
         <v>0.2307992734407124</v>
@@ -905,13 +905,13 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>0.4747116077277396</v>
+        <v>2.283812157809734</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4524914868175983</v>
+        <v>2.287677649408579</v>
       </c>
       <c r="G20" t="n">
-        <v>6.080933970212937</v>
+        <v>9.012051125057042</v>
       </c>
       <c r="H20" t="n">
         <v>0.3447703079265707</v>
@@ -925,13 +925,13 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>0.7534885611385107</v>
+        <v>2.147204767380442</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7357200253754854</v>
+        <v>3.555896525084973</v>
       </c>
       <c r="G21" t="n">
-        <v>6.628975462700639</v>
+        <v>6.688662008515426</v>
       </c>
       <c r="H21" t="n">
         <v>0.2074131825938821</v>

--- a/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times_success.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-9/map-bf-9_times_success.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>bf</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>bf-seq</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -478,6 +483,9 @@
       <c r="H2" t="n">
         <v>0.4582752680778504</v>
       </c>
+      <c r="I2" t="n">
+        <v>1.257664906829596</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -504,6 +512,9 @@
       <c r="H3" t="n">
         <v>0.3540511178970337</v>
       </c>
+      <c r="I3" t="n">
+        <v>0.8568585384264589</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -530,6 +541,9 @@
       <c r="H4" t="n">
         <v>0.315459703207016</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.6752389370650053</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -556,6 +570,9 @@
       <c r="H5" t="n">
         <v>0.3047110742330551</v>
       </c>
+      <c r="I5" t="n">
+        <v>0.8894357065856456</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -582,6 +599,9 @@
       <c r="H6" t="n">
         <v>0.3350402837991714</v>
       </c>
+      <c r="I6" t="n">
+        <v>0.4635359591990709</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -608,6 +628,9 @@
       <c r="H7" t="n">
         <v>0.3732976883649826</v>
       </c>
+      <c r="I7" t="n">
+        <v>0.6848957301676273</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -634,6 +657,9 @@
       <c r="H8" t="n">
         <v>0.4728059631586075</v>
       </c>
+      <c r="I8" t="n">
+        <v>0.7376334971189499</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -660,6 +686,9 @@
       <c r="H9" t="n">
         <v>0.3602443265914917</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.5673317218571902</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -686,6 +715,9 @@
       <c r="H10" t="n">
         <v>0.3005736583471298</v>
       </c>
+      <c r="I10" t="n">
+        <v>0.2732098084688186</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -712,6 +744,9 @@
       <c r="H11" t="n">
         <v>0.2494030541181564</v>
       </c>
+      <c r="I11" t="n">
+        <v>0.2017023532092571</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -738,6 +773,9 @@
       <c r="H12" t="n">
         <v>0.3432255566120148</v>
       </c>
+      <c r="I12" t="n">
+        <v>0.2878326430916786</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -764,6 +802,9 @@
       <c r="H13" t="n">
         <v>0.3173182178288698</v>
       </c>
+      <c r="I13" t="n">
+        <v>0.2915828852759053</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -790,6 +831,9 @@
       <c r="H14" t="n">
         <v>0.3379825606294301</v>
       </c>
+      <c r="I14" t="n">
+        <v>0.3341206591981261</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -815,6 +859,9 @@
       </c>
       <c r="H15" t="n">
         <v>0.3049165198336477</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3444174623683743</v>
       </c>
     </row>
     <row r="16">
@@ -836,6 +883,9 @@
       <c r="H16" t="n">
         <v>0.5247801759026267</v>
       </c>
+      <c r="I16" t="n">
+        <v>0.2034415484998714</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -856,6 +906,9 @@
       <c r="H17" t="n">
         <v>0.2200568526983261</v>
       </c>
+      <c r="I17" t="n">
+        <v>0.1130235953256488</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -876,6 +929,9 @@
       <c r="H18" t="n">
         <v>1.73492241948843</v>
       </c>
+      <c r="I18" t="n">
+        <v>0.2023052357137203</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -896,6 +952,9 @@
       <c r="H19" t="n">
         <v>0.2307992734407124</v>
       </c>
+      <c r="I19" t="n">
+        <v>0.2259275567178664</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -916,6 +975,9 @@
       <c r="H20" t="n">
         <v>0.3447703079265707</v>
       </c>
+      <c r="I20" t="n">
+        <v>0.6052067219553625</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -936,6 +998,9 @@
       <c r="H21" t="n">
         <v>0.2074131825938821</v>
       </c>
+      <c r="I21" t="n">
+        <v>0.2989832585444674</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
